--- a/assets/data/excel/wildStages.xlsx
+++ b/assets/data/excel/wildStages.xlsx
@@ -592,10 +592,9 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E010", "level": 2}, {"enemyId": "E004", "level": 2}, {"enemyId": "E006", "level": 3}]</t>
+          <t>[{"enemyId": "E_M010", "level": 2}, {"enemyId": "E_M004", "level": 2}, {"enemyId": "E_M006", "level": 3}]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,7 +607,6 @@
           <t>[{"type": "exp", "amount": 60}, {"type": "mycelium", "amount": 35}]</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -637,7 +635,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 3}, {"enemyId": "E006", "level": 3}, {"enemyId": "E010", "level": 4}]</t>
+          <t>[{"enemyId": "E_M003", "level": 3}, {"enemyId": "E_M006", "level": 3}, {"enemyId": "E_M010", "level": 4}]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -650,7 +648,6 @@
           <t>[{"type": "exp", "amount": 70}, {"type": "mycelium", "amount": 40}]</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -679,7 +676,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 4}, {"enemyId": "E004", "level": 4}, {"enemyId": "E002", "level": 5}]</t>
+          <t>[{"enemyId": "E_M008", "level": 4}, {"enemyId": "E_M004", "level": 4}, {"enemyId": "E_M002", "level": 5}]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,7 +689,6 @@
           <t>[{"type": "exp", "amount": 80}, {"type": "mycelium", "amount": 45}]</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -721,7 +717,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 5}, {"enemyId": "E004", "level": 5}, {"enemyId": "E009", "level": 6}]</t>
+          <t>[{"enemyId": "E_M001", "level": 5}, {"enemyId": "E_M004", "level": 5}, {"enemyId": "E_M009", "level": 6}]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -734,7 +730,6 @@
           <t>[{"type": "exp", "amount": 90}, {"type": "mycelium", "amount": 50}]</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -763,7 +758,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E010", "level": 6}, {"enemyId": "E006", "level": 6}, {"enemyId": "E002", "level": 7}]</t>
+          <t>[{"enemyId": "E_M010", "level": 6}, {"enemyId": "E_M006", "level": 6}, {"enemyId": "E_M002", "level": 7}]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -809,7 +804,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 7}, {"enemyId": "E001", "level": 7}, {"enemyId": "E010", "level": 8}]</t>
+          <t>[{"enemyId": "E_M008", "level": 7}, {"enemyId": "E_M001", "level": 7}, {"enemyId": "E_M010", "level": 8}]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -822,7 +817,6 @@
           <t>[{"type": "exp", "amount": 110}, {"type": "mycelium", "amount": 60}]</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -851,7 +845,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 8}, {"enemyId": "E007", "level": 8}, {"enemyId": "E008", "level": 9}]</t>
+          <t>[{"enemyId": "E_M004", "level": 8}, {"enemyId": "E_M007", "level": 8}, {"enemyId": "E_M008", "level": 9}]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -864,7 +858,6 @@
           <t>[{"type": "exp", "amount": 120}, {"type": "mycelium", "amount": 65}]</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -893,7 +886,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 9}, {"enemyId": "E002", "level": 9}, {"enemyId": "E007", "level": 10}]</t>
+          <t>[{"enemyId": "E_M003", "level": 9}, {"enemyId": "E_M002", "level": 9}, {"enemyId": "E_M007", "level": 10}]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -906,7 +899,6 @@
           <t>[{"type": "exp", "amount": 130}, {"type": "mycelium", "amount": 70}]</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -935,7 +927,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 10}, {"enemyId": "E004", "level": 10}, {"enemyId": "E008", "level": 11}]</t>
+          <t>[{"enemyId": "E_M005", "level": 10}, {"enemyId": "E_M004", "level": 10}, {"enemyId": "E_M008", "level": 11}]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -948,7 +940,6 @@
           <t>[{"type": "exp", "amount": 140}, {"type": "mycelium", "amount": 75}]</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -977,7 +968,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 11}, {"enemyId": "E004", "level": 11}, {"enemyId": "E010", "level": 12}]</t>
+          <t>[{"enemyId": "E_M007", "level": 11}, {"enemyId": "E_M004", "level": 11}, {"enemyId": "E_M010", "level": 12}]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1016,10 +1007,9 @@
       <c r="E14" t="n">
         <v>11</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 12}, {"enemyId": "E006", "level": 12}, {"enemyId": "E007", "level": 13}]</t>
+          <t>[{"enemyId": "E_M002", "level": 12}, {"enemyId": "E_M006", "level": 12}, {"enemyId": "E_M007", "level": 13}]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1032,7 +1022,6 @@
           <t>[{"type": "exp", "amount": 90}, {"type": "mycelium", "amount": 55}]</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1061,7 +1050,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 13}, {"enemyId": "E008", "level": 13}, {"enemyId": "E010", "level": 14}]</t>
+          <t>[{"enemyId": "E_M007", "level": 13}, {"enemyId": "E_M008", "level": 13}, {"enemyId": "E_M010", "level": 14}]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1074,7 +1063,6 @@
           <t>[{"type": "exp", "amount": 100}, {"type": "mycelium", "amount": 60}]</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1103,7 +1091,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 14}, {"enemyId": "E001", "level": 14}, {"enemyId": "E008", "level": 15}]</t>
+          <t>[{"enemyId": "E_M002", "level": 14}, {"enemyId": "E_M001", "level": 14}, {"enemyId": "E_M008", "level": 15}]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1116,7 +1104,6 @@
           <t>[{"type": "exp", "amount": 110}, {"type": "mycelium", "amount": 65}]</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1145,7 +1132,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 15}, {"enemyId": "E002", "level": 15}, {"enemyId": "E004", "level": 16}]</t>
+          <t>[{"enemyId": "E_M007", "level": 15}, {"enemyId": "E_M002", "level": 15}, {"enemyId": "E_M004", "level": 16}]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1158,7 +1145,6 @@
           <t>[{"type": "exp", "amount": 120}, {"type": "mycelium", "amount": 70}]</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1187,7 +1173,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 16}, {"enemyId": "E008", "level": 16}, {"enemyId": "E002", "level": 17}]</t>
+          <t>[{"enemyId": "E_M007", "level": 16}, {"enemyId": "E_M008", "level": 16}, {"enemyId": "E_M002", "level": 17}]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1233,7 +1219,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 17}, {"enemyId": "E002", "level": 17}, {"enemyId": "E005", "level": 18}]</t>
+          <t>[{"enemyId": "E_M001", "level": 17}, {"enemyId": "E_M002", "level": 17}, {"enemyId": "E_M005", "level": 18}]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1246,7 +1232,6 @@
           <t>[{"type": "exp", "amount": 140}, {"type": "mycelium", "amount": 80}]</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1275,7 +1260,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 18}, {"enemyId": "E004", "level": 18}, {"enemyId": "E003", "level": 19}]</t>
+          <t>[{"enemyId": "E_M009", "level": 18}, {"enemyId": "E_M004", "level": 18}, {"enemyId": "E_M003", "level": 19}]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1288,7 +1273,6 @@
           <t>[{"type": "exp", "amount": 150}, {"type": "mycelium", "amount": 85}]</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1317,7 +1301,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 19}, {"enemyId": "E009", "level": 19}, {"enemyId": "E004", "level": 20}]</t>
+          <t>[{"enemyId": "E_M005", "level": 19}, {"enemyId": "E_M009", "level": 19}, {"enemyId": "E_M004", "level": 20}]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1330,7 +1314,6 @@
           <t>[{"type": "exp", "amount": 160}, {"type": "mycelium", "amount": 90}]</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1359,7 +1342,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 20}, {"enemyId": "E001", "level": 20}, {"enemyId": "E003", "level": 21}]</t>
+          <t>[{"enemyId": "E_M009", "level": 20}, {"enemyId": "E_M001", "level": 20}, {"enemyId": "E_M003", "level": 21}]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1372,7 +1355,6 @@
           <t>[{"type": "exp", "amount": 170}, {"type": "mycelium", "amount": 95}]</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1401,7 +1383,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 21}, {"enemyId": "E001", "level": 21}, {"enemyId": "E010", "level": 22}]</t>
+          <t>[{"enemyId": "E_M007", "level": 21}, {"enemyId": "E_M001", "level": 21}, {"enemyId": "E_M010", "level": 22}]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1440,10 +1422,9 @@
       <c r="E24" t="n">
         <v>21</v>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 22}, {"enemyId": "E008", "level": 22}, {"enemyId": "E009", "level": 23}]</t>
+          <t>[{"enemyId": "E_M007", "level": 22}, {"enemyId": "E_M008", "level": 22}, {"enemyId": "E_M009", "level": 23}]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1456,7 +1437,6 @@
           <t>[{"type": "exp", "amount": 120}, {"type": "mycelium", "amount": 75}]</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1485,7 +1465,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 23}, {"enemyId": "E010", "level": 23}, {"enemyId": "E007", "level": 24}]</t>
+          <t>[{"enemyId": "E_M009", "level": 23}, {"enemyId": "E_M010", "level": 23}, {"enemyId": "E_M007", "level": 24}]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1498,7 +1478,6 @@
           <t>[{"type": "exp", "amount": 130}, {"type": "mycelium", "amount": 80}]</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1527,7 +1506,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 24}, {"enemyId": "E004", "level": 24}, {"enemyId": "E009", "level": 25}]</t>
+          <t>[{"enemyId": "E_M001", "level": 24}, {"enemyId": "E_M004", "level": 24}, {"enemyId": "E_M009", "level": 25}]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1540,7 +1519,6 @@
           <t>[{"type": "exp", "amount": 140}, {"type": "mycelium", "amount": 85}]</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1569,7 +1547,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 25}, {"enemyId": "E004", "level": 25}, {"enemyId": "E007", "level": 26}]</t>
+          <t>[{"enemyId": "E_M003", "level": 25}, {"enemyId": "E_M004", "level": 25}, {"enemyId": "E_M007", "level": 26}]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1582,7 +1560,6 @@
           <t>[{"type": "exp", "amount": 150}, {"type": "mycelium", "amount": 90}]</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1611,7 +1588,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 26}, {"enemyId": "E007", "level": 26}, {"enemyId": "E005", "level": 27}]</t>
+          <t>[{"enemyId": "E_M003", "level": 26}, {"enemyId": "E_M007", "level": 26}, {"enemyId": "E_M005", "level": 27}]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1657,7 +1634,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 27}, {"enemyId": "E009", "level": 27}, {"enemyId": "E004", "level": 28}]</t>
+          <t>[{"enemyId": "E_M007", "level": 27}, {"enemyId": "E_M009", "level": 27}, {"enemyId": "E_M004", "level": 28}]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1670,7 +1647,6 @@
           <t>[{"type": "exp", "amount": 170}, {"type": "mycelium", "amount": 100}]</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1699,7 +1675,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 28}, {"enemyId": "E005", "level": 28}, {"enemyId": "E010", "level": 29}]</t>
+          <t>[{"enemyId": "E_M009", "level": 28}, {"enemyId": "E_M005", "level": 28}, {"enemyId": "E_M010", "level": 29}]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1712,7 +1688,6 @@
           <t>[{"type": "exp", "amount": 180}, {"type": "mycelium", "amount": 105}]</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1741,7 +1716,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 29}, {"enemyId": "E010", "level": 29}, {"enemyId": "E007", "level": 30}]</t>
+          <t>[{"enemyId": "E_M003", "level": 29}, {"enemyId": "E_M010", "level": 29}, {"enemyId": "E_M007", "level": 30}]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1754,7 +1729,6 @@
           <t>[{"type": "exp", "amount": 190}, {"type": "mycelium", "amount": 110}]</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1783,7 +1757,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 30}, {"enemyId": "E005", "level": 30}, {"enemyId": "E001", "level": 31}]</t>
+          <t>[{"enemyId": "E_M002", "level": 30}, {"enemyId": "E_M005", "level": 30}, {"enemyId": "E_M001", "level": 31}]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1796,7 +1770,6 @@
           <t>[{"type": "exp", "amount": 200}, {"type": "mycelium", "amount": 115}]</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1825,7 +1798,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 31}, {"enemyId": "E002", "level": 31}, {"enemyId": "E004", "level": 32}]</t>
+          <t>[{"enemyId": "E_M009", "level": 31}, {"enemyId": "E_M002", "level": 31}, {"enemyId": "E_M004", "level": 32}]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1864,10 +1837,9 @@
       <c r="E34" t="n">
         <v>31</v>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 32}, {"enemyId": "E002", "level": 32}, {"enemyId": "E007", "level": 33}]</t>
+          <t>[{"enemyId": "E_M008", "level": 32}, {"enemyId": "E_M002", "level": 32}, {"enemyId": "E_M007", "level": 33}]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1880,7 +1852,6 @@
           <t>[{"type": "exp", "amount": 150}, {"type": "mycelium", "amount": 95}]</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1909,7 +1880,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 33}, {"enemyId": "E002", "level": 33}, {"enemyId": "E007", "level": 34}]</t>
+          <t>[{"enemyId": "E_M008", "level": 33}, {"enemyId": "E_M002", "level": 33}, {"enemyId": "E_M007", "level": 34}]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1922,7 +1893,6 @@
           <t>[{"type": "exp", "amount": 160}, {"type": "mycelium", "amount": 100}]</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1951,7 +1921,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 34}, {"enemyId": "E006", "level": 34}, {"enemyId": "E001", "level": 35}]</t>
+          <t>[{"enemyId": "E_M004", "level": 34}, {"enemyId": "E_M006", "level": 34}, {"enemyId": "E_M001", "level": 35}]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1964,7 +1934,6 @@
           <t>[{"type": "exp", "amount": 170}, {"type": "mycelium", "amount": 105}]</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1993,7 +1962,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 35}, {"enemyId": "E007", "level": 35}, {"enemyId": "E001", "level": 36}]</t>
+          <t>[{"enemyId": "E_M002", "level": 35}, {"enemyId": "E_M007", "level": 35}, {"enemyId": "E_M001", "level": 36}]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2006,7 +1975,6 @@
           <t>[{"type": "exp", "amount": 180}, {"type": "mycelium", "amount": 110}]</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2035,7 +2003,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 36}, {"enemyId": "E003", "level": 36}, {"enemyId": "E008", "level": 37}]</t>
+          <t>[{"enemyId": "E_M001", "level": 36}, {"enemyId": "E_M003", "level": 36}, {"enemyId": "E_M008", "level": 37}]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2081,7 +2049,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 37}, {"enemyId": "E010", "level": 37}, {"enemyId": "E009", "level": 38}]</t>
+          <t>[{"enemyId": "E_M007", "level": 37}, {"enemyId": "E_M010", "level": 37}, {"enemyId": "E_M009", "level": 38}]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2094,7 +2062,6 @@
           <t>[{"type": "exp", "amount": 200}, {"type": "mycelium", "amount": 120}]</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2123,7 +2090,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 38}, {"enemyId": "E005", "level": 38}, {"enemyId": "E007", "level": 39}]</t>
+          <t>[{"enemyId": "E_M002", "level": 38}, {"enemyId": "E_M005", "level": 38}, {"enemyId": "E_M007", "level": 39}]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2136,7 +2103,6 @@
           <t>[{"type": "exp", "amount": 210}, {"type": "mycelium", "amount": 125}]</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2165,7 +2131,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 39}, {"enemyId": "E005", "level": 39}, {"enemyId": "E004", "level": 40}]</t>
+          <t>[{"enemyId": "E_M008", "level": 39}, {"enemyId": "E_M005", "level": 39}, {"enemyId": "E_M004", "level": 40}]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2178,7 +2144,6 @@
           <t>[{"type": "exp", "amount": 220}, {"type": "mycelium", "amount": 130}]</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2207,7 +2172,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 40}, {"enemyId": "E010", "level": 40}, {"enemyId": "E008", "level": 41}]</t>
+          <t>[{"enemyId": "E_M009", "level": 40}, {"enemyId": "E_M010", "level": 40}, {"enemyId": "E_M008", "level": 41}]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2220,7 +2185,6 @@
           <t>[{"type": "exp", "amount": 230}, {"type": "mycelium", "amount": 135}]</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2249,7 +2213,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 41}, {"enemyId": "E005", "level": 41}, {"enemyId": "E001", "level": 42}]</t>
+          <t>[{"enemyId": "E_M003", "level": 41}, {"enemyId": "E_M005", "level": 41}, {"enemyId": "E_M001", "level": 42}]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2288,10 +2252,9 @@
       <c r="E44" t="n">
         <v>41</v>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 42}, {"enemyId": "E006", "level": 42}, {"enemyId": "E004", "level": 43}]</t>
+          <t>[{"enemyId": "E_M005", "level": 42}, {"enemyId": "E_M006", "level": 42}, {"enemyId": "E_M004", "level": 43}]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2304,7 +2267,6 @@
           <t>[{"type": "exp", "amount": 180}, {"type": "mycelium", "amount": 115}]</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2333,7 +2295,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 43}, {"enemyId": "E006", "level": 43}, {"enemyId": "E003", "level": 44}]</t>
+          <t>[{"enemyId": "E_M009", "level": 43}, {"enemyId": "E_M006", "level": 43}, {"enemyId": "E_M003", "level": 44}]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2346,7 +2308,6 @@
           <t>[{"type": "exp", "amount": 190}, {"type": "mycelium", "amount": 120}]</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2375,7 +2336,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 44}, {"enemyId": "E010", "level": 44}, {"enemyId": "E006", "level": 45}]</t>
+          <t>[{"enemyId": "E_M003", "level": 44}, {"enemyId": "E_M010", "level": 44}, {"enemyId": "E_M006", "level": 45}]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2388,7 +2349,6 @@
           <t>[{"type": "exp", "amount": 200}, {"type": "mycelium", "amount": 125}]</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2417,7 +2377,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 45}, {"enemyId": "E006", "level": 45}, {"enemyId": "E001", "level": 46}]</t>
+          <t>[{"enemyId": "E_M008", "level": 45}, {"enemyId": "E_M006", "level": 45}, {"enemyId": "E_M001", "level": 46}]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2430,7 +2390,6 @@
           <t>[{"type": "exp", "amount": 210}, {"type": "mycelium", "amount": 130}]</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2459,7 +2418,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 46}, {"enemyId": "E005", "level": 46}, {"enemyId": "E009", "level": 47}]</t>
+          <t>[{"enemyId": "E_M003", "level": 46}, {"enemyId": "E_M005", "level": 46}, {"enemyId": "E_M009", "level": 47}]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2505,7 +2464,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 47}, {"enemyId": "E005", "level": 47}, {"enemyId": "E007", "level": 48}]</t>
+          <t>[{"enemyId": "E_M008", "level": 47}, {"enemyId": "E_M005", "level": 47}, {"enemyId": "E_M007", "level": 48}]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2518,7 +2477,6 @@
           <t>[{"type": "exp", "amount": 230}, {"type": "mycelium", "amount": 140}]</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2547,7 +2505,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 48}, {"enemyId": "E003", "level": 48}, {"enemyId": "E010", "level": 49}]</t>
+          <t>[{"enemyId": "E_M008", "level": 48}, {"enemyId": "E_M003", "level": 48}, {"enemyId": "E_M010", "level": 49}]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2560,7 +2518,6 @@
           <t>[{"type": "exp", "amount": 240}, {"type": "mycelium", "amount": 145}]</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2589,7 +2546,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 49}, {"enemyId": "E007", "level": 49}, {"enemyId": "E008", "level": 50}]</t>
+          <t>[{"enemyId": "E_M009", "level": 49}, {"enemyId": "E_M007", "level": 49}, {"enemyId": "E_M008", "level": 50}]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2602,7 +2559,6 @@
           <t>[{"type": "exp", "amount": 250}, {"type": "mycelium", "amount": 150}]</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2631,7 +2587,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 50}, {"enemyId": "E004", "level": 50}, {"enemyId": "E003", "level": 51}]</t>
+          <t>[{"enemyId": "E_M007", "level": 50}, {"enemyId": "E_M004", "level": 50}, {"enemyId": "E_M003", "level": 51}]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2644,7 +2600,6 @@
           <t>[{"type": "exp", "amount": 260}, {"type": "mycelium", "amount": 155}]</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2673,7 +2628,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 51}, {"enemyId": "E005", "level": 51}, {"enemyId": "E007", "level": 52}]</t>
+          <t>[{"enemyId": "E_M009", "level": 51}, {"enemyId": "E_M005", "level": 51}, {"enemyId": "E_M007", "level": 52}]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2712,10 +2667,9 @@
       <c r="E54" t="n">
         <v>51</v>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 52}, {"enemyId": "E008", "level": 53}, {"enemyId": "E015", "level": 53}]</t>
+          <t>[{"enemyId": "E_M007", "level": 52}, {"enemyId": "E_M008", "level": 53}, {"enemyId": "E_L005", "level": 53}]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2728,7 +2682,6 @@
           <t>[{"type": "exp", "amount": 210}, {"type": "mycelium", "amount": 135}]</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2757,7 +2710,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 53}, {"enemyId": "E010", "level": 54}, {"enemyId": "E018", "level": 54}]</t>
+          <t>[{"enemyId": "E_M005", "level": 53}, {"enemyId": "E_M010", "level": 54}, {"enemyId": "E_L008", "level": 54}]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2770,7 +2723,6 @@
           <t>[{"type": "exp", "amount": 220}, {"type": "mycelium", "amount": 140}]</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2799,7 +2751,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 54}, {"enemyId": "E001", "level": 55}, {"enemyId": "E017", "level": 55}]</t>
+          <t>[{"enemyId": "E_M009", "level": 54}, {"enemyId": "E_M001", "level": 55}, {"enemyId": "E_L007", "level": 55}]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2812,7 +2764,6 @@
           <t>[{"type": "exp", "amount": 230}, {"type": "mycelium", "amount": 145}]</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2841,7 +2792,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 55}, {"enemyId": "E005", "level": 56}, {"enemyId": "E018", "level": 56}]</t>
+          <t>[{"enemyId": "E_M001", "level": 55}, {"enemyId": "E_M005", "level": 56}, {"enemyId": "E_L008", "level": 56}]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2854,7 +2805,6 @@
           <t>[{"type": "exp", "amount": 240}, {"type": "mycelium", "amount": 150}]</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2883,7 +2833,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 56}, {"enemyId": "E002", "level": 57}, {"enemyId": "E017", "level": 57}]</t>
+          <t>[{"enemyId": "E_M003", "level": 56}, {"enemyId": "E_M002", "level": 57}, {"enemyId": "E_L007", "level": 57}]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2929,7 +2879,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 57}, {"enemyId": "E010", "level": 58}, {"enemyId": "E018", "level": 58}]</t>
+          <t>[{"enemyId": "E_M009", "level": 57}, {"enemyId": "E_M010", "level": 58}, {"enemyId": "E_L008", "level": 58}]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2942,7 +2892,6 @@
           <t>[{"type": "exp", "amount": 260}, {"type": "mycelium", "amount": 160}]</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2971,7 +2920,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 58}, {"enemyId": "E009", "level": 59}, {"enemyId": "E015", "level": 59}]</t>
+          <t>[{"enemyId": "E_M002", "level": 58}, {"enemyId": "E_M009", "level": 59}, {"enemyId": "E_L005", "level": 59}]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2984,7 +2933,6 @@
           <t>[{"type": "exp", "amount": 270}, {"type": "mycelium", "amount": 165}]</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3013,7 +2961,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 59}, {"enemyId": "E006", "level": 60}, {"enemyId": "E019", "level": 60}]</t>
+          <t>[{"enemyId": "E_M003", "level": 59}, {"enemyId": "E_M006", "level": 60}, {"enemyId": "E_L009", "level": 60}]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3026,7 +2974,6 @@
           <t>[{"type": "exp", "amount": 280}, {"type": "mycelium", "amount": 170}]</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3055,7 +3002,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 60}, {"enemyId": "E004", "level": 61}, {"enemyId": "E012", "level": 61}]</t>
+          <t>[{"enemyId": "E_M007", "level": 60}, {"enemyId": "E_M004", "level": 61}, {"enemyId": "E_L002", "level": 61}]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3068,7 +3015,6 @@
           <t>[{"type": "exp", "amount": 290}, {"type": "mycelium", "amount": 175}]</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3097,7 +3043,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 61}, {"enemyId": "E007", "level": 62}, {"enemyId": "E013", "level": 62}]</t>
+          <t>[{"enemyId": "E_M005", "level": 61}, {"enemyId": "E_M007", "level": 62}, {"enemyId": "E_L003", "level": 62}]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3136,10 +3082,9 @@
       <c r="E64" t="n">
         <v>61</v>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 62}, {"enemyId": "E007", "level": 63}, {"enemyId": "E018", "level": 63}]</t>
+          <t>[{"enemyId": "E_M008", "level": 62}, {"enemyId": "E_M007", "level": 63}, {"enemyId": "E_L008", "level": 63}]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3152,7 +3097,6 @@
           <t>[{"type": "exp", "amount": 240}, {"type": "mycelium", "amount": 155}]</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3181,7 +3125,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 63}, {"enemyId": "E004", "level": 64}, {"enemyId": "E015", "level": 64}]</t>
+          <t>[{"enemyId": "E_M007", "level": 63}, {"enemyId": "E_M004", "level": 64}, {"enemyId": "E_L005", "level": 64}]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3194,7 +3138,6 @@
           <t>[{"type": "exp", "amount": 250}, {"type": "mycelium", "amount": 160}]</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3223,7 +3166,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 64}, {"enemyId": "E007", "level": 65}, {"enemyId": "E017", "level": 65}]</t>
+          <t>[{"enemyId": "E_M009", "level": 64}, {"enemyId": "E_M007", "level": 65}, {"enemyId": "E_L007", "level": 65}]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3236,7 +3179,6 @@
           <t>[{"type": "exp", "amount": 260}, {"type": "mycelium", "amount": 165}]</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3265,7 +3207,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 65}, {"enemyId": "E004", "level": 66}, {"enemyId": "E020", "level": 66}]</t>
+          <t>[{"enemyId": "E_M009", "level": 65}, {"enemyId": "E_M004", "level": 66}, {"enemyId": "E_L010", "level": 66}]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3278,7 +3220,6 @@
           <t>[{"type": "exp", "amount": 270}, {"type": "mycelium", "amount": 170}]</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3307,7 +3248,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E010", "level": 66}, {"enemyId": "E002", "level": 67}, {"enemyId": "E011", "level": 67}]</t>
+          <t>[{"enemyId": "E_M010", "level": 66}, {"enemyId": "E_M002", "level": 67}, {"enemyId": "E_L001", "level": 67}]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3353,7 +3294,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 67}, {"enemyId": "E010", "level": 68}, {"enemyId": "E011", "level": 68}]</t>
+          <t>[{"enemyId": "E_M008", "level": 67}, {"enemyId": "E_M010", "level": 68}, {"enemyId": "E_L001", "level": 68}]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3366,7 +3307,6 @@
           <t>[{"type": "exp", "amount": 290}, {"type": "mycelium", "amount": 180}]</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3395,7 +3335,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 68}, {"enemyId": "E002", "level": 69}, {"enemyId": "E011", "level": 69}]</t>
+          <t>[{"enemyId": "E_M003", "level": 68}, {"enemyId": "E_M002", "level": 69}, {"enemyId": "E_L001", "level": 69}]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3408,7 +3348,6 @@
           <t>[{"type": "exp", "amount": 300}, {"type": "mycelium", "amount": 185}]</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3437,7 +3376,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E006", "level": 69}, {"enemyId": "E002", "level": 70}, {"enemyId": "E018", "level": 70}]</t>
+          <t>[{"enemyId": "E_M006", "level": 69}, {"enemyId": "E_M002", "level": 70}, {"enemyId": "E_L008", "level": 70}]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3450,7 +3389,6 @@
           <t>[{"type": "exp", "amount": 310}, {"type": "mycelium", "amount": 190}]</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3479,7 +3417,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E010", "level": 70}, {"enemyId": "E001", "level": 71}, {"enemyId": "E020", "level": 71}]</t>
+          <t>[{"enemyId": "E_M010", "level": 70}, {"enemyId": "E_M001", "level": 71}, {"enemyId": "E_L010", "level": 71}]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3492,7 +3430,6 @@
           <t>[{"type": "exp", "amount": 320}, {"type": "mycelium", "amount": 195}]</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3521,7 +3458,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E007", "level": 71}, {"enemyId": "E001", "level": 72}, {"enemyId": "E019", "level": 72}]</t>
+          <t>[{"enemyId": "E_M007", "level": 71}, {"enemyId": "E_M001", "level": 72}, {"enemyId": "E_L009", "level": 72}]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3560,10 +3497,9 @@
       <c r="E74" t="n">
         <v>71</v>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 72}, {"enemyId": "E005", "level": 73}, {"enemyId": "E011", "level": 73}]</t>
+          <t>[{"enemyId": "E_M002", "level": 72}, {"enemyId": "E_M005", "level": 73}, {"enemyId": "E_L001", "level": 73}]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3576,7 +3512,6 @@
           <t>[{"type": "exp", "amount": 270}, {"type": "mycelium", "amount": 175}]</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3605,7 +3540,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 73}, {"enemyId": "E007", "level": 74}, {"enemyId": "E017", "level": 74}]</t>
+          <t>[{"enemyId": "E_M009", "level": 73}, {"enemyId": "E_M007", "level": 74}, {"enemyId": "E_L007", "level": 74}]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3618,7 +3553,6 @@
           <t>[{"type": "exp", "amount": 280}, {"type": "mycelium", "amount": 180}]</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3647,7 +3581,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 74}, {"enemyId": "E005", "level": 75}, {"enemyId": "E019", "level": 75}]</t>
+          <t>[{"enemyId": "E_M009", "level": 74}, {"enemyId": "E_M005", "level": 75}, {"enemyId": "E_L009", "level": 75}]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3660,7 +3594,6 @@
           <t>[{"type": "exp", "amount": 290}, {"type": "mycelium", "amount": 185}]</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3689,7 +3622,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 75}, {"enemyId": "E006", "level": 76}, {"enemyId": "E013", "level": 76}]</t>
+          <t>[{"enemyId": "E_M005", "level": 75}, {"enemyId": "E_M006", "level": 76}, {"enemyId": "E_L003", "level": 76}]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3702,7 +3635,6 @@
           <t>[{"type": "exp", "amount": 300}, {"type": "mycelium", "amount": 190}]</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3731,7 +3663,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E006", "level": 76}, {"enemyId": "E004", "level": 77}, {"enemyId": "E020", "level": 77}]</t>
+          <t>[{"enemyId": "E_M006", "level": 76}, {"enemyId": "E_M004", "level": 77}, {"enemyId": "E_L010", "level": 77}]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3777,7 +3709,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 77}, {"enemyId": "E009", "level": 78}, {"enemyId": "E015", "level": 78}]</t>
+          <t>[{"enemyId": "E_M002", "level": 77}, {"enemyId": "E_M009", "level": 78}, {"enemyId": "E_L005", "level": 78}]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3790,7 +3722,6 @@
           <t>[{"type": "exp", "amount": 320}, {"type": "mycelium", "amount": 200}]</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3819,7 +3750,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 78}, {"enemyId": "E003", "level": 79}, {"enemyId": "E013", "level": 79}]</t>
+          <t>[{"enemyId": "E_M009", "level": 78}, {"enemyId": "E_M003", "level": 79}, {"enemyId": "E_L003", "level": 79}]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3832,7 +3763,6 @@
           <t>[{"type": "exp", "amount": 330}, {"type": "mycelium", "amount": 205}]</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3861,7 +3791,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 79}, {"enemyId": "E010", "level": 80}, {"enemyId": "E013", "level": 80}]</t>
+          <t>[{"enemyId": "E_M001", "level": 79}, {"enemyId": "E_M010", "level": 80}, {"enemyId": "E_L003", "level": 80}]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3874,7 +3804,6 @@
           <t>[{"type": "exp", "amount": 340}, {"type": "mycelium", "amount": 210}]</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3903,7 +3832,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 80}, {"enemyId": "E009", "level": 81}, {"enemyId": "E020", "level": 81}]</t>
+          <t>[{"enemyId": "E_M005", "level": 80}, {"enemyId": "E_M009", "level": 81}, {"enemyId": "E_L010", "level": 81}]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3916,7 +3845,6 @@
           <t>[{"type": "exp", "amount": 350}, {"type": "mycelium", "amount": 215}]</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3945,7 +3873,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 81}, {"enemyId": "E001", "level": 82}, {"enemyId": "E013", "level": 82}]</t>
+          <t>[{"enemyId": "E_M002", "level": 81}, {"enemyId": "E_M001", "level": 82}, {"enemyId": "E_L003", "level": 82}]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3984,10 +3912,9 @@
       <c r="E84" t="n">
         <v>81</v>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 82}, {"enemyId": "E002", "level": 83}, {"enemyId": "E016", "level": 83}]</t>
+          <t>[{"enemyId": "E_M009", "level": 82}, {"enemyId": "E_M002", "level": 83}, {"enemyId": "E_L006", "level": 83}]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4000,7 +3927,6 @@
           <t>[{"type": "exp", "amount": 300}, {"type": "mycelium", "amount": 195}]</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4029,7 +3955,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 83}, {"enemyId": "E010", "level": 84}, {"enemyId": "E018", "level": 84}]</t>
+          <t>[{"enemyId": "E_M001", "level": 83}, {"enemyId": "E_M010", "level": 84}, {"enemyId": "E_L008", "level": 84}]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4042,7 +3968,6 @@
           <t>[{"type": "exp", "amount": 310}, {"type": "mycelium", "amount": 200}]</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4071,7 +3996,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 84}, {"enemyId": "E005", "level": 85}, {"enemyId": "E013", "level": 85}]</t>
+          <t>[{"enemyId": "E_M003", "level": 84}, {"enemyId": "E_M005", "level": 85}, {"enemyId": "E_L003", "level": 85}]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4084,7 +4009,6 @@
           <t>[{"type": "exp", "amount": 320}, {"type": "mycelium", "amount": 205}]</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4113,7 +4037,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 85}, {"enemyId": "E007", "level": 86}, {"enemyId": "E013", "level": 86}]</t>
+          <t>[{"enemyId": "E_M008", "level": 85}, {"enemyId": "E_M007", "level": 86}, {"enemyId": "E_L003", "level": 86}]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4126,7 +4050,6 @@
           <t>[{"type": "exp", "amount": 330}, {"type": "mycelium", "amount": 210}]</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4155,7 +4078,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 86}, {"enemyId": "E001", "level": 87}, {"enemyId": "E011", "level": 87}]</t>
+          <t>[{"enemyId": "E_M002", "level": 86}, {"enemyId": "E_M001", "level": 87}, {"enemyId": "E_L001", "level": 87}]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4201,7 +4124,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 87}, {"enemyId": "E007", "level": 88}, {"enemyId": "E014", "level": 88}]</t>
+          <t>[{"enemyId": "E_M004", "level": 87}, {"enemyId": "E_M007", "level": 88}, {"enemyId": "E_L004", "level": 88}]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4214,7 +4137,6 @@
           <t>[{"type": "exp", "amount": 350}, {"type": "mycelium", "amount": 220}]</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4243,7 +4165,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 88}, {"enemyId": "E003", "level": 89}, {"enemyId": "E020", "level": 89}]</t>
+          <t>[{"enemyId": "E_M004", "level": 88}, {"enemyId": "E_M003", "level": 89}, {"enemyId": "E_L010", "level": 89}]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4256,7 +4178,6 @@
           <t>[{"type": "exp", "amount": 360}, {"type": "mycelium", "amount": 225}]</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4285,7 +4206,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 89}, {"enemyId": "E008", "level": 90}, {"enemyId": "E019", "level": 90}]</t>
+          <t>[{"enemyId": "E_M004", "level": 89}, {"enemyId": "E_M008", "level": 90}, {"enemyId": "E_L009", "level": 90}]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4298,7 +4219,6 @@
           <t>[{"type": "exp", "amount": 370}, {"type": "mycelium", "amount": 230}]</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4327,7 +4247,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 90}, {"enemyId": "E003", "level": 91}, {"enemyId": "E014", "level": 91}]</t>
+          <t>[{"enemyId": "E_M005", "level": 90}, {"enemyId": "E_M003", "level": 91}, {"enemyId": "E_L004", "level": 91}]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4340,7 +4260,6 @@
           <t>[{"type": "exp", "amount": 380}, {"type": "mycelium", "amount": 235}]</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4369,7 +4288,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 91}, {"enemyId": "E008", "level": 92}, {"enemyId": "E014", "level": 92}]</t>
+          <t>[{"enemyId": "E_M001", "level": 91}, {"enemyId": "E_M008", "level": 92}, {"enemyId": "E_L004", "level": 92}]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4408,10 +4327,9 @@
       <c r="E94" t="n">
         <v>91</v>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E010", "level": 92}, {"enemyId": "E001", "level": 93}, {"enemyId": "E016", "level": 93}]</t>
+          <t>[{"enemyId": "E_M010", "level": 92}, {"enemyId": "E_M001", "level": 93}, {"enemyId": "E_L006", "level": 93}]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4424,7 +4342,6 @@
           <t>[{"type": "exp", "amount": 330}, {"type": "mycelium", "amount": 215}]</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4453,7 +4370,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E001", "level": 93}, {"enemyId": "E009", "level": 94}, {"enemyId": "E016", "level": 94}]</t>
+          <t>[{"enemyId": "E_M001", "level": 93}, {"enemyId": "E_M009", "level": 94}, {"enemyId": "E_L006", "level": 94}]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4466,7 +4383,6 @@
           <t>[{"type": "exp", "amount": 340}, {"type": "mycelium", "amount": 220}]</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4495,7 +4411,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E002", "level": 94}, {"enemyId": "E009", "level": 95}, {"enemyId": "E014", "level": 95}]</t>
+          <t>[{"enemyId": "E_M002", "level": 94}, {"enemyId": "E_M009", "level": 95}, {"enemyId": "E_L004", "level": 95}]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4508,7 +4424,6 @@
           <t>[{"type": "exp", "amount": 350}, {"type": "mycelium", "amount": 225}]</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4537,7 +4452,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 95}, {"enemyId": "E001", "level": 96}, {"enemyId": "E020", "level": 96}]</t>
+          <t>[{"enemyId": "E_M009", "level": 95}, {"enemyId": "E_M001", "level": 96}, {"enemyId": "E_L010", "level": 96}]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4550,7 +4465,6 @@
           <t>[{"type": "exp", "amount": 360}, {"type": "mycelium", "amount": 230}]</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4579,7 +4493,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E008", "level": 96}, {"enemyId": "E001", "level": 97}, {"enemyId": "E012", "level": 97}]</t>
+          <t>[{"enemyId": "E_M008", "level": 96}, {"enemyId": "E_M001", "level": 97}, {"enemyId": "E_L002", "level": 97}]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4625,7 +4539,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E009", "level": 97}, {"enemyId": "E007", "level": 98}, {"enemyId": "E012", "level": 98}]</t>
+          <t>[{"enemyId": "E_M009", "level": 97}, {"enemyId": "E_M007", "level": 98}, {"enemyId": "E_L002", "level": 98}]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4638,7 +4552,6 @@
           <t>[{"type": "exp", "amount": 380}, {"type": "mycelium", "amount": 240}]</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4667,7 +4580,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E004", "level": 98}, {"enemyId": "E002", "level": 99}, {"enemyId": "E017", "level": 99}]</t>
+          <t>[{"enemyId": "E_M004", "level": 98}, {"enemyId": "E_M002", "level": 99}, {"enemyId": "E_L007", "level": 99}]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4680,7 +4593,6 @@
           <t>[{"type": "exp", "amount": 390}, {"type": "mycelium", "amount": 245}]</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4709,7 +4621,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 99}, {"enemyId": "E009", "level": 100}, {"enemyId": "E017", "level": 100}]</t>
+          <t>[{"enemyId": "E_M003", "level": 99}, {"enemyId": "E_M009", "level": 100}, {"enemyId": "E_L007", "level": 100}]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4722,7 +4634,6 @@
           <t>[{"type": "exp", "amount": 400}, {"type": "mycelium", "amount": 250}]</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4751,7 +4662,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E005", "level": 100}, {"enemyId": "E003", "level": 101}, {"enemyId": "E017", "level": 101}]</t>
+          <t>[{"enemyId": "E_M005", "level": 100}, {"enemyId": "E_M003", "level": 101}, {"enemyId": "E_L007", "level": 101}]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4764,7 +4675,6 @@
           <t>[{"type": "exp", "amount": 410}, {"type": "mycelium", "amount": 255}]</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4793,7 +4703,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[{"enemyId": "E003", "level": 101}, {"enemyId": "E008", "level": 102}, {"enemyId": "E018", "level": 102}]</t>
+          <t>[{"enemyId": "E_M003", "level": 101}, {"enemyId": "E_M008", "level": 102}, {"enemyId": "E_L008", "level": 102}]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
